--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,6 +134,10 @@
   </si>
   <si>
     <t>DPS特效战力系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -466,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
@@ -712,6 +716,59 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>1.25</v>
+      </c>
+      <c r="I7">
+        <v>62.5</v>
+      </c>
+      <c r="J7">
+        <v>1.25</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -138,6 +138,14 @@
   </si>
   <si>
     <t>弓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对塔伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -470,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
@@ -488,7 +496,7 @@
     <col min="18" max="18" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,8 +551,11 @@
       <c r="R1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -599,18 +610,21 @@
       <c r="R2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="S2" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -662,8 +676,11 @@
       <c r="R5">
         <v>0</v>
       </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>24</v>
       </c>
@@ -715,8 +732,11 @@
       <c r="R6">
         <v>0.3</v>
       </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -767,6 +787,9 @@
       </c>
       <c r="R7">
         <v>0.3</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="55">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,22 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>紫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质颜色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弓箭手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>角色名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,15 +117,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>弓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对塔伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里填写英雄一级时的情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猴赛雷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动加攻速，没有特效伤害，但都加载了基础攻击上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土肉肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰肉肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火肉肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>壮壮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>撞撞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆爆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒液</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秒秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>职业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坦克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺客</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -153,7 +245,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +258,13 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -195,9 +294,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -478,322 +578,1055 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.25" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.25" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="V4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="I5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1.2</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0.1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>60</v>
+      </c>
+      <c r="I6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1.2</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1.2</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0.1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>60</v>
+      </c>
+      <c r="I8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1.2</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>70</v>
+      </c>
+      <c r="I9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1.2</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0.2</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>70</v>
+      </c>
+      <c r="I10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="K10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1.2</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="V10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>80</v>
+      </c>
+      <c r="I11">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1.2</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>96</v>
+      </c>
+      <c r="I12">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1.2</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>112</v>
+      </c>
+      <c r="I13">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J13">
+        <v>11</v>
+      </c>
+      <c r="K13">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1.2</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>0.1</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14">
+        <v>20</v>
+      </c>
+      <c r="G14">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
+      <c r="H14">
+        <v>67</v>
+      </c>
+      <c r="I14">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1.2</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>0.1</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15">
         <v>20</v>
       </c>
-      <c r="F5">
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>80</v>
+      </c>
+      <c r="I15">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1.2</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0.15</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>94</v>
+      </c>
+      <c r="I16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J16">
+        <v>14</v>
+      </c>
+      <c r="K16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1.2</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0.15</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
-      <c r="G5">
-        <v>120</v>
-      </c>
-      <c r="H5">
-        <v>1.25</v>
-      </c>
-      <c r="I5">
-        <v>13.3</v>
-      </c>
-      <c r="J5">
-        <v>1.25</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>0.25</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6">
+      <c r="H17">
+        <v>56</v>
+      </c>
+      <c r="I17">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J17">
+        <v>11</v>
+      </c>
+      <c r="K17">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1.2</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0.2</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18">
         <v>20</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-      <c r="H6">
-        <v>1.25</v>
-      </c>
-      <c r="I6">
-        <v>62.5</v>
-      </c>
-      <c r="J6">
-        <v>1.25</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0.3</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7">
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>67</v>
+      </c>
+      <c r="I18">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J18">
+        <v>11</v>
+      </c>
+      <c r="K18">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1.2</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0.2</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19">
         <v>20</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7">
-        <v>1.25</v>
-      </c>
-      <c r="I7">
-        <v>62.5</v>
-      </c>
-      <c r="J7">
-        <v>1.25</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0.3</v>
-      </c>
-      <c r="S7">
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
+        <v>78</v>
+      </c>
+      <c r="I19">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J19">
+        <v>15</v>
+      </c>
+      <c r="K19">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1.2</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0.1</v>
+      </c>
+      <c r="T19">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="57">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,6 +238,14 @@
   </si>
   <si>
     <t>刺客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,92 +586,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.25" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.625" customWidth="1"/>
+    <col min="1" max="2" width="8.25" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="15.125" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -672,13 +683,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
@@ -717,910 +728,958 @@
         <v>9</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>51</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>20</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>4</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="I5">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="J5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K5">
         <v>8</v>
       </c>
-      <c r="K5">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="L5">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
       <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
         <v>1.2</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>0.1</v>
       </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="s">
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="W5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>51</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>20</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>60</v>
       </c>
-      <c r="I6">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="J6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="K6">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>1.2</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>51</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>50</v>
       </c>
-      <c r="I7">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="J7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="K7">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="L7">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
         <v>4</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
       <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>1.2</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>0.1</v>
       </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="U7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>51</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>20</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>4</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>60</v>
       </c>
-      <c r="I8">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="J8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K8">
         <v>10</v>
       </c>
-      <c r="K8">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="L8">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
         <v>4</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
       <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <v>1.2</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>36</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>51</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>20</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>70</v>
       </c>
-      <c r="I9">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="J9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K9">
         <v>8</v>
       </c>
-      <c r="K9">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="L9">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
       <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
         <v>1.2</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
       <c r="R9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>0.2</v>
       </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="U9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>1007</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>80</v>
+      </c>
+      <c r="J10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K10">
+        <v>8</v>
+      </c>
+      <c r="L10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1.2</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>1008</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>96</v>
+      </c>
+      <c r="J11">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1.2</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>1009</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>112</v>
+      </c>
+      <c r="J12">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K12">
+        <v>11</v>
+      </c>
+      <c r="L12">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1.2</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>0.1</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D13" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E13" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F13" t="s">
         <v>51</v>
       </c>
-      <c r="F10">
+      <c r="G13">
         <v>20</v>
       </c>
-      <c r="G10">
+      <c r="H13">
         <v>4</v>
       </c>
-      <c r="H10">
+      <c r="I13">
         <v>70</v>
       </c>
-      <c r="I10">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J10">
+      <c r="J13">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K13">
         <v>9</v>
       </c>
-      <c r="K10">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
+      <c r="L13">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
         <v>4</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
         <v>1.2</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="W13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
         <v>15</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11">
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
         <v>20</v>
       </c>
-      <c r="G11">
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14">
+        <v>67</v>
+      </c>
+      <c r="J14">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K14">
         <v>10</v>
       </c>
-      <c r="H11">
+      <c r="L14">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1.2</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>0.1</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
         <v>80</v>
       </c>
-      <c r="I11">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-      <c r="K11">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
+      <c r="J15">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
         <v>1.2</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0.15</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>1014</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12">
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
         <v>20</v>
       </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <v>96</v>
-      </c>
-      <c r="I12">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J12">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>67</v>
+      </c>
+      <c r="J16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K16">
+        <v>11</v>
+      </c>
+      <c r="L16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
         <v>1.2</v>
       </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0.2</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>1015</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
         <v>15</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E17" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13">
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
         <v>20</v>
       </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13">
-        <v>112</v>
-      </c>
-      <c r="I13">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J13">
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>78</v>
+      </c>
+      <c r="J17">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K17">
+        <v>15</v>
+      </c>
+      <c r="L17">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1.2</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0.1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>1012</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>7</v>
+      </c>
+      <c r="I18">
+        <v>94</v>
+      </c>
+      <c r="J18">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K18">
+        <v>14</v>
+      </c>
+      <c r="L18">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1.2</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0.15</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>1013</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>56</v>
+      </c>
+      <c r="J19">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K19">
         <v>11</v>
       </c>
-      <c r="K13">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
+      <c r="L19">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
         <v>1.2</v>
       </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <v>0.1</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14">
-        <v>20</v>
-      </c>
-      <c r="G14">
-        <v>7</v>
-      </c>
-      <c r="H14">
-        <v>67</v>
-      </c>
-      <c r="I14">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J14">
-        <v>10</v>
-      </c>
-      <c r="K14">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>1.2</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>0.1</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
-      <c r="G15">
-        <v>7</v>
-      </c>
-      <c r="H15">
-        <v>80</v>
-      </c>
-      <c r="I15">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J15">
-        <v>10</v>
-      </c>
-      <c r="K15">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>1.2</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0.15</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16">
-        <v>20</v>
-      </c>
-      <c r="G16">
-        <v>7</v>
-      </c>
-      <c r="H16">
-        <v>94</v>
-      </c>
-      <c r="I16">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J16">
-        <v>14</v>
-      </c>
-      <c r="K16">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>1.2</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0.15</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17">
-        <v>20</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17">
-        <v>56</v>
-      </c>
-      <c r="I17">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J17">
-        <v>11</v>
-      </c>
-      <c r="K17">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>1.2</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
         <v>0.2</v>
       </c>
-      <c r="T17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18">
-        <v>20</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-      <c r="H18">
-        <v>67</v>
-      </c>
-      <c r="I18">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J18">
-        <v>11</v>
-      </c>
-      <c r="K18">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>1.2</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0.2</v>
-      </c>
-      <c r="T18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19">
-        <v>20</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19">
-        <v>78</v>
-      </c>
-      <c r="I19">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J19">
-        <v>15</v>
-      </c>
-      <c r="K19">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>1.2</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0.1</v>
-      </c>
-      <c r="T19">
+      <c r="U19">
         <v>1</v>
       </c>
     </row>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1045,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="Q11">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -1231,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="Q15">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -1482,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="Q18">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>1</v>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色初始属性表.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="英雄初始属性" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">英雄初始属性!$A$1:$W$19</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -589,7 +592,8 @@
   <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="8.25" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
@@ -609,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -674,10 +678,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -748,11 +752,11 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
         <v>1001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -767,16 +771,16 @@
         <v>20</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J5">
         <v>1.1499999999999999</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L5">
         <v>1.1499999999999999</v>
@@ -813,11 +817,11 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
         <v>1002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -832,22 +836,22 @@
         <v>20</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J6">
         <v>1.1499999999999999</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>1.1499999999999999</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -875,11 +879,11 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
         <v>1003</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -894,16 +898,16 @@
         <v>20</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J7">
         <v>1.1499999999999999</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>1.1499999999999999</v>
@@ -937,11 +941,11 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
         <v>1004</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -956,22 +960,22 @@
         <v>20</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J8">
         <v>1.1499999999999999</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L8">
         <v>1.1499999999999999</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -999,11 +1003,11 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
         <v>1005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
@@ -1018,22 +1022,22 @@
         <v>20</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J9">
         <v>1.1499999999999999</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L9">
         <v>1.1499999999999999</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -1061,11 +1065,11 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
         <v>1007</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -1080,16 +1084,16 @@
         <v>20</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="J10">
         <v>1.1499999999999999</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="L10">
         <v>1.1499999999999999</v>
@@ -1123,11 +1127,11 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
         <v>1008</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1142,16 +1146,16 @@
         <v>20</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="J11">
         <v>1.1499999999999999</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L11">
         <v>1.1499999999999999</v>
@@ -1185,11 +1189,11 @@
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12">
         <v>1009</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1204,16 +1208,16 @@
         <v>20</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="J12">
         <v>1.1499999999999999</v>
       </c>
       <c r="K12">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="L12">
         <v>1.1499999999999999</v>
@@ -1247,11 +1251,11 @@
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
         <v>1006</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -1266,22 +1270,22 @@
         <v>20</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J13">
         <v>1.1499999999999999</v>
       </c>
       <c r="K13">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="L13">
         <v>1.1499999999999999</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -1312,11 +1316,11 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14">
         <v>1010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -1331,16 +1335,16 @@
         <v>20</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="J14">
         <v>1.1499999999999999</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L14">
         <v>1.1499999999999999</v>
@@ -1374,11 +1378,11 @@
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15">
         <v>1011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1393,22 +1397,22 @@
         <v>20</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="J15">
         <v>1.1499999999999999</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L15">
         <v>1.1499999999999999</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1436,11 +1440,11 @@
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16">
         <v>1014</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -1455,22 +1459,22 @@
         <v>20</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="J16">
         <v>1.1499999999999999</v>
       </c>
       <c r="K16">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L16">
         <v>1.1499999999999999</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -1498,11 +1502,11 @@
       </c>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17">
         <v>1015</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -1517,22 +1521,22 @@
         <v>20</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="J17">
         <v>1.1499999999999999</v>
       </c>
       <c r="K17">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="L17">
         <v>1.1499999999999999</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -1560,11 +1564,11 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
         <v>1012</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -1579,22 +1583,22 @@
         <v>20</v>
       </c>
       <c r="H18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>1.1499999999999999</v>
       </c>
       <c r="K18">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="L18">
         <v>1.1499999999999999</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -1622,11 +1626,11 @@
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19">
         <v>1013</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -1641,22 +1645,22 @@
         <v>20</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="J19">
         <v>1.1499999999999999</v>
       </c>
       <c r="K19">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L19">
         <v>1.1499999999999999</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -1684,6 +1688,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W19"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
